--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260717.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260717.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>19.52%</t>
+          <t>18.93%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.41%</t>
+          <t>6.97%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.90%</t>
         </is>
       </c>
     </row>
@@ -682,117 +682,117 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>7,064,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>7,064,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7,800,000</t>
+          <t>1,650,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,140,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>1,140,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.16%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>2,700,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>2,170,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>6,940,000</t>
+          <t>6,934,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>94,500</t>
+          <t>171,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1525,78 +1525,78 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>7,306,156,280</t>
+          <t>6,152,764,703</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-2,114,099,395</t>
+          <t>-689,112,873</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
